--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488286_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488286_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0396</v>
+        <v>3.5671</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3881</v>
+        <v>3.5954</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3484</v>
+        <v>-0.0284</v>
       </c>
       <c r="G2" t="n">
         <v>3.556</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9779</v>
+        <v>-0.4505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2014</v>
+        <v>0.0059</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7765</v>
+        <v>-0.4564</v>
       </c>
       <c r="V2" t="n">
         <v>1.5733</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. REYES BARRANCO</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1534</v>
+        <v>1.7536</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1879</v>
+        <v>1.7478</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0345</v>
+        <v>0.0058</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1434</v>
+        <v>1.0044</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.4367</v>
+        <v>-1.2581</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5801</v>
+        <v>2.2624</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0809</v>
+        <v>2.3966</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8293</v>
+        <v>0.2187</v>
       </c>
       <c r="L3" t="n">
-        <v>3.9102</v>
+        <v>2.1779</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9375</v>
+        <v>-1.3922</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6074</v>
+        <v>-1.4768</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3301</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0382</v>
+        <v>-0.1853</v>
       </c>
       <c r="R3" t="n">
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2689</v>
+        <v>-0.4747</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8307</v>
+        <v>-0.4635</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4382</v>
+        <v>-0.0112</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2589</v>
+        <v>-0.6289</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5733</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.0843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7637</v>
+        <v>0.4267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15</v>
+        <v>-0.3424</v>
       </c>
       <c r="G4" t="n">
         <v>1.2005</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8419</v>
+        <v>0.0124</v>
       </c>
       <c r="T4" t="n">
-        <v>0.102</v>
+        <v>-0.235</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7399</v>
+        <v>0.2474</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9433</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>J. REYES BARRANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6687</v>
+        <v>0.0067</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0076</v>
+        <v>1.3613</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3389</v>
+        <v>-1.3546</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0044</v>
+        <v>1.1434</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2581</v>
+        <v>-2.4367</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2624</v>
+        <v>3.5801</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3966</v>
+        <v>3.0809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2187</v>
+        <v>-0.8293</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1779</v>
+        <v>3.9102</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3922</v>
+        <v>-1.9375</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4768</v>
+        <v>-1.6074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.3301</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="R5" t="n">
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5596</v>
+        <v>0.1222</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2037</v>
+        <v>0.0041</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3559</v>
+        <v>0.1181</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1419</v>
+        <v>-0.0911</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5582</v>
+        <v>1.2759</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4163</v>
+        <v>-1.367</v>
       </c>
       <c r="G6" t="n">
         <v>-3.346</v>
@@ -922,13 +922,13 @@
         <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2532</v>
+        <v>-0.4862</v>
       </c>
       <c r="T6" t="n">
-        <v>0.342</v>
+        <v>0.0597</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5952</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.8883</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1604</v>
+        <v>-0.4151</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5006</v>
+        <v>0.8528</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.661</v>
+        <v>-1.2679</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2252</v>
+        <v>-3.0359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.365</v>
+        <v>-4.7945</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8602</v>
+        <v>1.7586</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2078</v>
+        <v>-1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0004</v>
+        <v>-2.7664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2074</v>
+        <v>1.5665</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0174</v>
+        <v>-1.8359</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6354</v>
+        <v>-2.0281</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6529</v>
+        <v>0.1922</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1273</v>
+        <v>-0.8969</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0721</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1995</v>
+        <v>-0.2674</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8877</v>
+        <v>3.1471</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2589</v>
+        <v>4.7204</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.1466</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.332</v>
+        <v>-1.1298</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.138</v>
+        <v>0.4574</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.194</v>
+        <v>-1.5872</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0359</v>
+        <v>1.2252</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.7945</v>
+        <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7586</v>
+        <v>0.8602</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2</v>
+        <v>1.2078</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.7664</v>
+        <v>1.0004</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5665</v>
+        <v>0.2074</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8359</v>
+        <v>0.0174</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0281</v>
+        <v>-0.6354</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1922</v>
+        <v>0.6529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8138</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6203</v>
+        <v>0.0289</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1935</v>
+        <v>-0.1256</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1471</v>
+        <v>-1.8877</v>
       </c>
       <c r="W8" t="n">
-        <v>4.7204</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5733</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2316</v>
+        <v>-4.0351</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7524</v>
+        <v>-1.6545</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4792</v>
+        <v>-2.3807</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7289</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8732</v>
+        <v>-0.6768</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5471</v>
+        <v>-0.4492</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3261</v>
+        <v>-0.2276</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8066000000000013</v>
+        <v>-0.2593999999999985</v>
       </c>
       <c r="E10" t="n">
-        <v>7.515700000000001</v>
+        <v>8.062800000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.3223</v>
+        <v>-8.3224</v>
       </c>
       <c r="G10" t="n">
         <v>-1.981300000000001</v>
@@ -1222,7 +1222,7 @@
         <v>-11.214</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9608999999999999</v>
+        <v>0.9609000000000001</v>
       </c>
       <c r="P10" t="n">
         <v>2.7794</v>
@@ -1234,10 +1234,10 @@
         <v>13.8967</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.494200000000001</v>
+        <v>-2.9472</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.2257</v>
+        <v>-1.6786</v>
       </c>
       <c r="U10" t="n">
         <v>-1.2686</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.731</v>
+        <v>6.1979</v>
       </c>
       <c r="E11" t="n">
-        <v>4.7859</v>
+        <v>4.5901</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9451</v>
+        <v>1.6078</v>
       </c>
       <c r="G11" t="n">
         <v>2.0714</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5571</v>
+        <v>1.024</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5397</v>
+        <v>0.3439</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0174</v>
+        <v>0.6802</v>
       </c>
       <c r="V11" t="n">
         <v>4.0289</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.6793</v>
+        <v>5.2624</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8326</v>
+        <v>4.5388</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8467</v>
+        <v>0.7236</v>
       </c>
       <c r="G12" t="n">
         <v>1.2446</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0085</v>
+        <v>0.5916</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3209</v>
+        <v>0.0271</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6877</v>
+        <v>0.5645</v>
       </c>
       <c r="V12" t="n">
         <v>1.5733</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9005</v>
+        <v>2.1904</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7418</v>
+        <v>2.0563</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1588</v>
+        <v>0.1341</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2706</v>
@@ -1468,13 +1468,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3565</v>
+        <v>0.6463</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0321</v>
+        <v>0.3466</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3243</v>
+        <v>0.2997</v>
       </c>
       <c r="V13" t="n">
         <v>1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7766</v>
+        <v>1.7343</v>
       </c>
       <c r="E14" t="n">
-        <v>0.761</v>
+        <v>0.8589</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0156</v>
+        <v>0.8753</v>
       </c>
       <c r="G14" t="n">
         <v>0.8191000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1537</v>
+        <v>1.1114</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2114</v>
+        <v>0.3094</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9423</v>
+        <v>0.802</v>
       </c>
       <c r="V14" t="n">
         <v>2.7684</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6339</v>
+        <v>-0.0659</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5235</v>
+        <v>-1.8467</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1574</v>
+        <v>1.7808</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2831</v>
+        <v>0.2089</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5258</v>
+        <v>1.8263</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2427</v>
+        <v>-1.6174</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0721</v>
+        <v>0.1616</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0306</v>
+        <v>0.773</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.789</v>
+        <v>0.0473</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5048</v>
+        <v>1.0533</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2841</v>
+        <v>-1.006</v>
       </c>
       <c r="P18" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1462</v>
+        <v>0.0958</v>
       </c>
       <c r="T18" t="n">
-        <v>0.434</v>
+        <v>-0.1554</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2878</v>
+        <v>0.2512</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6926</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6792</v>
+        <v>-0.5274</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2384</v>
+        <v>1.4256</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5592</v>
+        <v>-1.953</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2089</v>
+        <v>0.2831</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8263</v>
+        <v>0.5258</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6174</v>
+        <v>-0.2427</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1616</v>
+        <v>1.0721</v>
       </c>
       <c r="K19" t="n">
-        <v>0.773</v>
+        <v>1.0306</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0473</v>
+        <v>-0.789</v>
       </c>
       <c r="N19" t="n">
-        <v>1.0533</v>
+        <v>-0.5048</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.006</v>
+        <v>-0.2841</v>
       </c>
       <c r="P19" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0.2528</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5471</v>
+        <v>0.3361</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0296</v>
+        <v>-0.0833</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6926</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.6365</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9978</v>
+        <v>-2.0706</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7201</v>
+        <v>0.5242</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7179</v>
+        <v>-2.5948</v>
       </c>
       <c r="G20" t="n">
         <v>0.4144</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1791</v>
+        <v>0.1063</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2151</v>
+        <v>0.0193</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0361</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-3.1471</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8296</v>
+        <v>-2.8301</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1024</v>
+        <v>-1.0044</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7272</v>
+        <v>-1.8257</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5713</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0562</v>
+        <v>0.0556</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2751</v>
+        <v>0.1766</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5733</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4656</v>
+        <v>-4.7452</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9643</v>
+        <v>-0.7684</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5012</v>
+        <v>-3.9767</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1247</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2422</v>
+        <v>0.4781</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1567</v>
+        <v>0.3526</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3989</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
         <v>-5.0986</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.9411</v>
+        <v>-4.9526</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0038</v>
+        <v>-3.3183</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9373</v>
+        <v>-1.6343</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3596</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2033</v>
+        <v>-0.2148</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8754</v>
+        <v>-0.1899</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3278</v>
+        <v>-0.0249</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0076</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8064999999999971</v>
+        <v>1.459499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.322300000000002</v>
+        <v>8.322399999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.515599999999999</v>
+        <v>-6.862900000000002</v>
       </c>
       <c r="G24" t="n">
         <v>1.9816</v>
@@ -2305,7 +2305,7 @@
         <v>11.2142</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9608</v>
+        <v>-0.9608000000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-8.271899999999999</v>
@@ -2326,13 +2326,13 @@
         <v>11.1174</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4942</v>
+        <v>4.1471</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2685</v>
+        <v>1.2688</v>
       </c>
       <c r="U24" t="n">
-        <v>2.225800000000001</v>
+        <v>2.8786</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8897</v>
